--- a/SGC-CKN/Excel/643b5028-63e3-4d98-b258-70ab84992a13_Lô_đất_ký_hiệu_CT-02_P8-2_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/643b5028-63e3-4d98-b258-70ab84992a13_Lô_đất_ký_hiệu_CT-02_P8-2_D800_22-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>12:30 21/03/2026</t>
+    <t>02:30 21/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>09:00 22/03/2026</t>
+    <t>09:00 21/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -98,11 +98,11 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">12:30
+    <t xml:space="preserve">02:30
 21/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14:00
+    <t xml:space="preserve">3:00
 21/03/2026</t>
   </si>
   <si>
@@ -115,17 +115,21 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">15:30
+    <t xml:space="preserve">03:00
 21/03/2026</t>
   </si>
   <si>
+    <t xml:space="preserve">03:30
+21/03/2026</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">16:40
+    <t xml:space="preserve">03:40
 21/03/2026</t>
   </si>
   <si>
@@ -135,7 +139,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">18:15
+    <t xml:space="preserve">04:15
 21/03/2026</t>
   </si>
   <si>
@@ -145,7 +149,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">19:30
+    <t xml:space="preserve">04:30
 21/03/2026</t>
   </si>
   <si>
@@ -155,7 +159,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">21:00
+    <t xml:space="preserve">05:00
 21/03/2026</t>
   </si>
   <si>
@@ -165,7 +169,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">22:10
+    <t xml:space="preserve">05:10
 21/03/2026</t>
   </si>
   <si>
@@ -175,7 +179,7 @@
     <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">23:10
+    <t xml:space="preserve">05:31
 21/03/2026</t>
   </si>
   <si>
@@ -186,7 +190,7 @@
   </si>
   <si>
     <t xml:space="preserve">08:20
-22/03/2026</t>
+21/03/2026</t>
   </si>
   <si>
     <t>chen sỏi</t>
@@ -199,7 +203,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:00
-22/03/2026</t>
+21/03/2026</t>
   </si>
   <si>
     <t>Kết thúc</t>
@@ -239,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -315,12 +319,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF134E4A"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -338,7 +336,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -377,12 +375,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7F3D0"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -413,11 +411,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -553,17 +546,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -622,22 +615,19 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1223,19 +1213,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="H11" s="5">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="J11" s="8">
-        <v>3.07</v>
+        <v>13</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1252,80 +1242,80 @@
         <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="G12" s="9">
         <v>-8.5</v>
       </c>
       <c r="H12" s="9">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="J12" s="8">
-        <v>1.67</v>
+        <v>2</v>
+      </c>
+      <c r="J12" s="12">
+        <v>4</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="12">
+      <c r="E13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="13">
         <v>-8.5</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <v>-16.8</v>
       </c>
-      <c r="H13" s="12">
-        <v>1.17</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="H13" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="I13" s="13">
         <v>8.3</v>
       </c>
-      <c r="J13" s="15">
-        <v>7.11</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="J13" s="8">
+        <v>49.8</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-16.8</v>
@@ -1334,13 +1324,13 @@
         <v>-22</v>
       </c>
       <c r="H14" s="16">
-        <v>1.58</v>
+        <v>0.58</v>
       </c>
       <c r="I14" s="16">
         <v>5.2</v>
       </c>
       <c r="J14" s="8">
-        <v>3.28</v>
+        <v>8.91</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1348,19 +1338,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-22</v>
@@ -1369,13 +1359,13 @@
         <v>-26.1</v>
       </c>
       <c r="H15" s="19">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="19">
         <v>4.1</v>
       </c>
       <c r="J15" s="8">
-        <v>3.28</v>
+        <v>16.4</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1383,34 +1373,34 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-26.1</v>
       </c>
       <c r="G16" s="22">
-        <v>-34.1</v>
+        <v>-34.2</v>
       </c>
       <c r="H16" s="22">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I16" s="22">
-        <v>8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>5.33</v>
+        <v>8.1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>16.2</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1418,34 +1408,34 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="25">
-        <v>-34.1</v>
+        <v>-34.2</v>
       </c>
       <c r="G17" s="25">
         <v>-37.1</v>
       </c>
       <c r="H17" s="25">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="I17" s="25">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="8">
-        <v>2.57</v>
+        <v>17.4</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1453,19 +1443,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-37.1</v>
@@ -1474,13 +1464,13 @@
         <v>-39.2</v>
       </c>
       <c r="H18" s="28">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="I18" s="28">
         <v>2.1</v>
       </c>
       <c r="J18" s="8">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1488,19 +1478,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="31">
         <v>-39.2</v>
@@ -1509,67 +1499,67 @@
         <v>-43.5</v>
       </c>
       <c r="H19" s="31">
-        <v>9.17</v>
+        <v>2.82</v>
       </c>
       <c r="I19" s="31">
         <v>4.3</v>
       </c>
-      <c r="J19" s="34">
-        <v>0.47</v>
+      <c r="J19" s="12">
+        <v>1.53</v>
       </c>
       <c r="K19" s="32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="35">
+      <c r="E20" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="34">
         <v>-43.5</v>
       </c>
-      <c r="G20" s="35">
-        <v>-44.85</v>
-      </c>
-      <c r="H20" s="35">
+      <c r="G20" s="34">
+        <v>-44.87</v>
+      </c>
+      <c r="H20" s="34">
         <v>0.67</v>
       </c>
-      <c r="I20" s="35">
-        <v>1.35</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2.03</v>
-      </c>
-      <c r="K20" s="36" t="s">
-        <v>59</v>
+      <c r="I20" s="34">
+        <v>1.37</v>
+      </c>
+      <c r="J20" s="12">
+        <v>2.05</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="A23" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1664,31 +1654,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1705,19 +1695,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="5">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="I2" s="8">
-        <v>3.07</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,48 +1724,48 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="F3" s="9">
         <v>-8.5</v>
       </c>
       <c r="G3" s="9">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="I3" s="8">
-        <v>1.67</v>
+        <v>2</v>
+      </c>
+      <c r="I3" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="C4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>-8.5</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>-16.8</v>
       </c>
-      <c r="G4" s="12">
-        <v>1.17</v>
-      </c>
-      <c r="H4" s="12">
+      <c r="G4" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="H4" s="13">
         <v>8.3</v>
       </c>
-      <c r="I4" s="15">
-        <v>7.11</v>
+      <c r="I4" s="8">
+        <v>49.8</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,7 +1776,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1798,13 +1788,13 @@
         <v>-22</v>
       </c>
       <c r="G5" s="16">
-        <v>1.58</v>
+        <v>0.58</v>
       </c>
       <c r="H5" s="16">
         <v>5.2</v>
       </c>
       <c r="I5" s="8">
-        <v>3.28</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1815,7 +1805,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1827,13 +1817,13 @@
         <v>-26.1</v>
       </c>
       <c r="G6" s="19">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="19">
         <v>4.1</v>
       </c>
       <c r="I6" s="8">
-        <v>3.28</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1844,7 +1834,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1853,16 +1843,16 @@
         <v>-26.1</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.1</v>
+        <v>-34.2</v>
       </c>
       <c r="G7" s="22">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="22">
-        <v>8</v>
-      </c>
-      <c r="I7" s="15">
-        <v>5.33</v>
+        <v>8.1</v>
+      </c>
+      <c r="I7" s="8">
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1873,25 +1863,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.1</v>
+        <v>-34.2</v>
       </c>
       <c r="F8" s="25">
         <v>-37.1</v>
       </c>
       <c r="G8" s="25">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="H8" s="25">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I8" s="8">
-        <v>2.57</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,7 +1892,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1914,13 +1904,13 @@
         <v>-39.2</v>
       </c>
       <c r="G9" s="28">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="28">
         <v>2.1</v>
       </c>
       <c r="I9" s="8">
-        <v>2.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1931,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1943,71 +1933,71 @@
         <v>-43.5</v>
       </c>
       <c r="G10" s="31">
-        <v>9.17</v>
+        <v>2.82</v>
       </c>
       <c r="H10" s="31">
         <v>4.3</v>
       </c>
-      <c r="I10" s="34">
-        <v>0.47</v>
+      <c r="I10" s="12">
+        <v>1.53</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="C11" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-43.5</v>
       </c>
-      <c r="F11" s="35">
-        <v>-44.85</v>
-      </c>
-      <c r="G11" s="35">
+      <c r="F11" s="34">
+        <v>-44.87</v>
+      </c>
+      <c r="G11" s="34">
         <v>0.67</v>
       </c>
-      <c r="H11" s="35">
-        <v>1.35</v>
-      </c>
-      <c r="I11" s="8">
-        <v>2.03</v>
+      <c r="H11" s="34">
+        <v>1.37</v>
+      </c>
+      <c r="I11" s="12">
+        <v>2.05</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="A12" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-1.4</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-44.85</v>
-      </c>
-      <c r="G12" s="40">
-        <v>20.5</v>
-      </c>
-      <c r="H12" s="40">
-        <v>43.45</v>
-      </c>
-      <c r="I12" s="40">
-        <v>2.12</v>
+      <c r="E12" s="39">
+        <v>0</v>
+      </c>
+      <c r="F12" s="39">
+        <v>-44.87</v>
+      </c>
+      <c r="G12" s="39">
+        <v>6.5</v>
+      </c>
+      <c r="H12" s="39">
+        <v>44.87</v>
+      </c>
+      <c r="I12" s="39">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
